--- a/data_lake/macro/South Korea/Consumer Price Index.xlsx
+++ b/data_lake/macro/South Korea/Consumer Price Index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BC0ECD-AD10-48BB-8E0D-C3C28A31AB7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFE81E8-F53C-4CC1-8C57-EE5D4BD3C9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="8">
   <si>
     <t>Base Date</t>
   </si>
@@ -437,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H680"/>
+  <dimension ref="A1:H681"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.296875" style="5" bestFit="1" customWidth="1"/>
@@ -15283,6 +15283,29 @@
       </c>
       <c r="H680" s="8"/>
     </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A681" s="5">
+        <v>46204</v>
+      </c>
+      <c r="B681" s="5">
+        <v>46238</v>
+      </c>
+      <c r="C681" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D681" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E681" s="11">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="F681" s="11">
+        <v>0.03</v>
+      </c>
+      <c r="G681" s="11">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G680">
     <sortCondition ref="B2:B680"/>

--- a/data_lake/macro/South Korea/Consumer Price Index.xlsx
+++ b/data_lake/macro/South Korea/Consumer Price Index.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/South Korea/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDFE81E8-F53C-4CC1-8C57-EE5D4BD3C9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54C4AD39-41FB-F944-B350-B0DA8B04044D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13160" yWindow="780" windowWidth="22840" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KOCPIY" sheetId="1" r:id="rId1"/>
+    <sheet name="info" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="19">
   <si>
     <t>Base Date</t>
   </si>
@@ -59,27 +60,68 @@
   <si>
     <t>UTC+9</t>
   </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ticker</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>URL</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Frequency</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Exchange</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country</t>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monthly</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>South Korea</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>KOCPIY</t>
+  </si>
+  <si>
+    <t>https://kr.investing.com/economic-calendar/south-korean-cpi-467</t>
+  </si>
+  <si>
+    <t>SK</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -98,21 +140,35 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -120,29 +176,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -156,10 +228,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="백분율" xfId="1" builtinId="5"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -437,19 +515,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H681"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H682"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.19921875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.796875" style="11" customWidth="1"/>
-    <col min="6" max="7" width="8.796875" style="11"/>
-    <col min="8" max="16384" width="8.796875" style="4"/>
+    <col min="5" max="5" width="8.83203125" style="11" customWidth="1"/>
+    <col min="6" max="7" width="8.83203125" style="11"/>
+    <col min="8" max="16384" width="8.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -472,7 +550,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>25538</v>
       </c>
@@ -490,7 +568,7 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>25569</v>
       </c>
@@ -511,7 +589,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>25600</v>
       </c>
@@ -532,7 +610,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>25628</v>
       </c>
@@ -553,7 +631,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>25659</v>
       </c>
@@ -574,7 +652,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>25689</v>
       </c>
@@ -595,7 +673,7 @@
       </c>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>25720</v>
       </c>
@@ -616,7 +694,7 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>25750</v>
       </c>
@@ -637,7 +715,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>25781</v>
       </c>
@@ -658,7 +736,7 @@
       </c>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>25812</v>
       </c>
@@ -679,7 +757,7 @@
       </c>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>25842</v>
       </c>
@@ -700,7 +778,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>25873</v>
       </c>
@@ -721,7 +799,7 @@
       </c>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>25903</v>
       </c>
@@ -742,7 +820,7 @@
       </c>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>25934</v>
       </c>
@@ -763,7 +841,7 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>25965</v>
       </c>
@@ -784,7 +862,7 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>25993</v>
       </c>
@@ -805,7 +883,7 @@
       </c>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>26024</v>
       </c>
@@ -826,7 +904,7 @@
       </c>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>26054</v>
       </c>
@@ -847,7 +925,7 @@
       </c>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>26085</v>
       </c>
@@ -868,7 +946,7 @@
       </c>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>26115</v>
       </c>
@@ -889,7 +967,7 @@
       </c>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>26146</v>
       </c>
@@ -910,7 +988,7 @@
       </c>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>26177</v>
       </c>
@@ -931,7 +1009,7 @@
       </c>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>26207</v>
       </c>
@@ -952,7 +1030,7 @@
       </c>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>26238</v>
       </c>
@@ -973,7 +1051,7 @@
       </c>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>26268</v>
       </c>
@@ -994,7 +1072,7 @@
       </c>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>26299</v>
       </c>
@@ -1015,7 +1093,7 @@
       </c>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>26330</v>
       </c>
@@ -1036,7 +1114,7 @@
       </c>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>26359</v>
       </c>
@@ -1057,7 +1135,7 @@
       </c>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>26390</v>
       </c>
@@ -1078,7 +1156,7 @@
       </c>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>26420</v>
       </c>
@@ -1099,7 +1177,7 @@
       </c>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>26451</v>
       </c>
@@ -1120,7 +1198,7 @@
       </c>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>26481</v>
       </c>
@@ -1141,7 +1219,7 @@
       </c>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>26512</v>
       </c>
@@ -1162,7 +1240,7 @@
       </c>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>26543</v>
       </c>
@@ -1183,7 +1261,7 @@
       </c>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>26573</v>
       </c>
@@ -1204,7 +1282,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>26604</v>
       </c>
@@ -1225,7 +1303,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>26634</v>
       </c>
@@ -1246,7 +1324,7 @@
       </c>
       <c r="H38" s="8"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>26665</v>
       </c>
@@ -1267,7 +1345,7 @@
       </c>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>26696</v>
       </c>
@@ -1288,7 +1366,7 @@
       </c>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="5">
         <v>26724</v>
       </c>
@@ -1309,7 +1387,7 @@
       </c>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>26755</v>
       </c>
@@ -1330,7 +1408,7 @@
       </c>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>26785</v>
       </c>
@@ -1351,7 +1429,7 @@
       </c>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>26816</v>
       </c>
@@ -1372,7 +1450,7 @@
       </c>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>26846</v>
       </c>
@@ -1393,7 +1471,7 @@
       </c>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>26877</v>
       </c>
@@ -1414,7 +1492,7 @@
       </c>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>26908</v>
       </c>
@@ -1435,7 +1513,7 @@
       </c>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>26938</v>
       </c>
@@ -1456,7 +1534,7 @@
       </c>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>26969</v>
       </c>
@@ -1477,7 +1555,7 @@
       </c>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>26999</v>
       </c>
@@ -1498,7 +1576,7 @@
       </c>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>27030</v>
       </c>
@@ -1519,7 +1597,7 @@
       </c>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>27061</v>
       </c>
@@ -1540,7 +1618,7 @@
       </c>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>27089</v>
       </c>
@@ -1561,7 +1639,7 @@
       </c>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>27120</v>
       </c>
@@ -1582,7 +1660,7 @@
       </c>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>27150</v>
       </c>
@@ -1603,7 +1681,7 @@
       </c>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>27181</v>
       </c>
@@ -1624,7 +1702,7 @@
       </c>
       <c r="H56" s="8"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>27211</v>
       </c>
@@ -1645,7 +1723,7 @@
       </c>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>27242</v>
       </c>
@@ -1666,7 +1744,7 @@
       </c>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>27273</v>
       </c>
@@ -1687,7 +1765,7 @@
       </c>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>27303</v>
       </c>
@@ -1708,7 +1786,7 @@
       </c>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>27334</v>
       </c>
@@ -1729,7 +1807,7 @@
       </c>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>27364</v>
       </c>
@@ -1750,7 +1828,7 @@
       </c>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>27395</v>
       </c>
@@ -1771,7 +1849,7 @@
       </c>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>27426</v>
       </c>
@@ -1792,7 +1870,7 @@
       </c>
       <c r="H64" s="8"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>27454</v>
       </c>
@@ -1813,7 +1891,7 @@
       </c>
       <c r="H65" s="8"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>27485</v>
       </c>
@@ -1834,7 +1912,7 @@
       </c>
       <c r="H66" s="8"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>27515</v>
       </c>
@@ -1855,7 +1933,7 @@
       </c>
       <c r="H67" s="8"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>27546</v>
       </c>
@@ -1876,7 +1954,7 @@
       </c>
       <c r="H68" s="8"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>27576</v>
       </c>
@@ -1897,7 +1975,7 @@
       </c>
       <c r="H69" s="8"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>27607</v>
       </c>
@@ -1918,7 +1996,7 @@
       </c>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>27638</v>
       </c>
@@ -1939,7 +2017,7 @@
       </c>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="5">
         <v>27668</v>
       </c>
@@ -1960,7 +2038,7 @@
       </c>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="5">
         <v>27699</v>
       </c>
@@ -1981,7 +2059,7 @@
       </c>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="5">
         <v>27729</v>
       </c>
@@ -2002,7 +2080,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="5">
         <v>27760</v>
       </c>
@@ -2023,7 +2101,7 @@
       </c>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="5">
         <v>27791</v>
       </c>
@@ -2044,7 +2122,7 @@
       </c>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>27820</v>
       </c>
@@ -2065,7 +2143,7 @@
       </c>
       <c r="H77" s="8"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>27851</v>
       </c>
@@ -2086,7 +2164,7 @@
       </c>
       <c r="H78" s="8"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>27881</v>
       </c>
@@ -2107,7 +2185,7 @@
       </c>
       <c r="H79" s="8"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>27912</v>
       </c>
@@ -2128,7 +2206,7 @@
       </c>
       <c r="H80" s="8"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>27942</v>
       </c>
@@ -2149,7 +2227,7 @@
       </c>
       <c r="H81" s="8"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>27973</v>
       </c>
@@ -2170,7 +2248,7 @@
       </c>
       <c r="H82" s="8"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>28004</v>
       </c>
@@ -2191,7 +2269,7 @@
       </c>
       <c r="H83" s="8"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>28034</v>
       </c>
@@ -2212,7 +2290,7 @@
       </c>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>28065</v>
       </c>
@@ -2233,7 +2311,7 @@
       </c>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>28095</v>
       </c>
@@ -2254,7 +2332,7 @@
       </c>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>28126</v>
       </c>
@@ -2275,7 +2353,7 @@
       </c>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>28157</v>
       </c>
@@ -2296,7 +2374,7 @@
       </c>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>28185</v>
       </c>
@@ -2317,7 +2395,7 @@
       </c>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <v>28216</v>
       </c>
@@ -2338,7 +2416,7 @@
       </c>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>28246</v>
       </c>
@@ -2359,7 +2437,7 @@
       </c>
       <c r="H91" s="8"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>28277</v>
       </c>
@@ -2380,7 +2458,7 @@
       </c>
       <c r="H92" s="8"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>28307</v>
       </c>
@@ -2401,7 +2479,7 @@
       </c>
       <c r="H93" s="8"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>28338</v>
       </c>
@@ -2422,7 +2500,7 @@
       </c>
       <c r="H94" s="8"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>28369</v>
       </c>
@@ -2443,7 +2521,7 @@
       </c>
       <c r="H95" s="8"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <v>28399</v>
       </c>
@@ -2464,7 +2542,7 @@
       </c>
       <c r="H96" s="8"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <v>28430</v>
       </c>
@@ -2485,7 +2563,7 @@
       </c>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <v>28460</v>
       </c>
@@ -2506,7 +2584,7 @@
       </c>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <v>28491</v>
       </c>
@@ -2527,7 +2605,7 @@
       </c>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <v>28522</v>
       </c>
@@ -2548,7 +2626,7 @@
       </c>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="5">
         <v>28550</v>
       </c>
@@ -2569,7 +2647,7 @@
       </c>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="5">
         <v>28581</v>
       </c>
@@ -2590,7 +2668,7 @@
       </c>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="5">
         <v>28611</v>
       </c>
@@ -2611,7 +2689,7 @@
       </c>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="5">
         <v>28642</v>
       </c>
@@ -2632,7 +2710,7 @@
       </c>
       <c r="H104" s="8"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="5">
         <v>28672</v>
       </c>
@@ -2653,7 +2731,7 @@
       </c>
       <c r="H105" s="8"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="5">
         <v>28703</v>
       </c>
@@ -2674,7 +2752,7 @@
       </c>
       <c r="H106" s="8"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="5">
         <v>28734</v>
       </c>
@@ -2695,7 +2773,7 @@
       </c>
       <c r="H107" s="8"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="5">
         <v>28764</v>
       </c>
@@ -2716,7 +2794,7 @@
       </c>
       <c r="H108" s="8"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="5">
         <v>28795</v>
       </c>
@@ -2737,7 +2815,7 @@
       </c>
       <c r="H109" s="8"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="5">
         <v>28825</v>
       </c>
@@ -2758,7 +2836,7 @@
       </c>
       <c r="H110" s="8"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="5">
         <v>28856</v>
       </c>
@@ -2779,7 +2857,7 @@
       </c>
       <c r="H111" s="8"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="5">
         <v>28887</v>
       </c>
@@ -2800,7 +2878,7 @@
       </c>
       <c r="H112" s="8"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="5">
         <v>28915</v>
       </c>
@@ -2821,7 +2899,7 @@
       </c>
       <c r="H113" s="8"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="5">
         <v>28946</v>
       </c>
@@ -2842,7 +2920,7 @@
       </c>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="5">
         <v>28976</v>
       </c>
@@ -2863,7 +2941,7 @@
       </c>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="5">
         <v>29007</v>
       </c>
@@ -2884,7 +2962,7 @@
       </c>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="5">
         <v>29037</v>
       </c>
@@ -2905,7 +2983,7 @@
       </c>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="5">
         <v>29068</v>
       </c>
@@ -2926,7 +3004,7 @@
       </c>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="5">
         <v>29099</v>
       </c>
@@ -2947,7 +3025,7 @@
       </c>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="5">
         <v>29129</v>
       </c>
@@ -2968,7 +3046,7 @@
       </c>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="5">
         <v>29160</v>
       </c>
@@ -2989,7 +3067,7 @@
       </c>
       <c r="H121" s="8"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="5">
         <v>29190</v>
       </c>
@@ -3010,7 +3088,7 @@
       </c>
       <c r="H122" s="8"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="5">
         <v>29221</v>
       </c>
@@ -3031,7 +3109,7 @@
       </c>
       <c r="H123" s="8"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="5">
         <v>29252</v>
       </c>
@@ -3052,7 +3130,7 @@
       </c>
       <c r="H124" s="8"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="5">
         <v>29281</v>
       </c>
@@ -3073,7 +3151,7 @@
       </c>
       <c r="H125" s="8"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="5">
         <v>29312</v>
       </c>
@@ -3094,7 +3172,7 @@
       </c>
       <c r="H126" s="8"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="5">
         <v>29342</v>
       </c>
@@ -3115,7 +3193,7 @@
       </c>
       <c r="H127" s="8"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="5">
         <v>29373</v>
       </c>
@@ -3136,7 +3214,7 @@
       </c>
       <c r="H128" s="8"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="5">
         <v>29403</v>
       </c>
@@ -3157,7 +3235,7 @@
       </c>
       <c r="H129" s="8"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="5">
         <v>29434</v>
       </c>
@@ -3178,7 +3256,7 @@
       </c>
       <c r="H130" s="8"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="5">
         <v>29465</v>
       </c>
@@ -3199,7 +3277,7 @@
       </c>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="5">
         <v>29495</v>
       </c>
@@ -3220,7 +3298,7 @@
       </c>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="5">
         <v>29526</v>
       </c>
@@ -3241,7 +3319,7 @@
       </c>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="5">
         <v>29556</v>
       </c>
@@ -3262,7 +3340,7 @@
       </c>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="5">
         <v>29587</v>
       </c>
@@ -3283,7 +3361,7 @@
       </c>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="5">
         <v>29618</v>
       </c>
@@ -3304,7 +3382,7 @@
       </c>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="5">
         <v>29646</v>
       </c>
@@ -3325,7 +3403,7 @@
       </c>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="5">
         <v>29677</v>
       </c>
@@ -3346,7 +3424,7 @@
       </c>
       <c r="H138" s="8"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="5">
         <v>29707</v>
       </c>
@@ -3367,7 +3445,7 @@
       </c>
       <c r="H139" s="8"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="5">
         <v>29738</v>
       </c>
@@ -3388,7 +3466,7 @@
       </c>
       <c r="H140" s="8"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="5">
         <v>29768</v>
       </c>
@@ -3409,7 +3487,7 @@
       </c>
       <c r="H141" s="8"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="5">
         <v>29799</v>
       </c>
@@ -3430,7 +3508,7 @@
       </c>
       <c r="H142" s="8"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="5">
         <v>29830</v>
       </c>
@@ -3451,7 +3529,7 @@
       </c>
       <c r="H143" s="8"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="5">
         <v>29860</v>
       </c>
@@ -3472,7 +3550,7 @@
       </c>
       <c r="H144" s="8"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="5">
         <v>29891</v>
       </c>
@@ -3493,7 +3571,7 @@
       </c>
       <c r="H145" s="8"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="5">
         <v>29921</v>
       </c>
@@ -3514,7 +3592,7 @@
       </c>
       <c r="H146" s="8"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="5">
         <v>29952</v>
       </c>
@@ -3535,7 +3613,7 @@
       </c>
       <c r="H147" s="8"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="5">
         <v>29983</v>
       </c>
@@ -3556,7 +3634,7 @@
       </c>
       <c r="H148" s="8"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="5">
         <v>30011</v>
       </c>
@@ -3577,7 +3655,7 @@
       </c>
       <c r="H149" s="8"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="5">
         <v>30042</v>
       </c>
@@ -3598,7 +3676,7 @@
       </c>
       <c r="H150" s="8"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="5">
         <v>30072</v>
       </c>
@@ -3619,7 +3697,7 @@
       </c>
       <c r="H151" s="8"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="5">
         <v>30103</v>
       </c>
@@ -3640,7 +3718,7 @@
       </c>
       <c r="H152" s="8"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="5">
         <v>30133</v>
       </c>
@@ -3661,7 +3739,7 @@
       </c>
       <c r="H153" s="8"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="5">
         <v>30164</v>
       </c>
@@ -3682,7 +3760,7 @@
       </c>
       <c r="H154" s="8"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="5">
         <v>30195</v>
       </c>
@@ -3703,7 +3781,7 @@
       </c>
       <c r="H155" s="8"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="5">
         <v>30225</v>
       </c>
@@ -3724,7 +3802,7 @@
       </c>
       <c r="H156" s="8"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="5">
         <v>30256</v>
       </c>
@@ -3745,7 +3823,7 @@
       </c>
       <c r="H157" s="8"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="5">
         <v>30286</v>
       </c>
@@ -3766,7 +3844,7 @@
       </c>
       <c r="H158" s="8"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="5">
         <v>30317</v>
       </c>
@@ -3787,7 +3865,7 @@
       </c>
       <c r="H159" s="8"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="5">
         <v>30348</v>
       </c>
@@ -3808,7 +3886,7 @@
       </c>
       <c r="H160" s="8"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="5">
         <v>30376</v>
       </c>
@@ -3829,7 +3907,7 @@
       </c>
       <c r="H161" s="8"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="5">
         <v>30407</v>
       </c>
@@ -3850,7 +3928,7 @@
       </c>
       <c r="H162" s="8"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="5">
         <v>30437</v>
       </c>
@@ -3871,7 +3949,7 @@
       </c>
       <c r="H163" s="8"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="5">
         <v>30468</v>
       </c>
@@ -3892,7 +3970,7 @@
       </c>
       <c r="H164" s="8"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="5">
         <v>30498</v>
       </c>
@@ -3913,7 +3991,7 @@
       </c>
       <c r="H165" s="8"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="5">
         <v>30529</v>
       </c>
@@ -3934,7 +4012,7 @@
       </c>
       <c r="H166" s="8"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="5">
         <v>30560</v>
       </c>
@@ -3955,7 +4033,7 @@
       </c>
       <c r="H167" s="8"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="5">
         <v>30590</v>
       </c>
@@ -3976,7 +4054,7 @@
       </c>
       <c r="H168" s="8"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="5">
         <v>30621</v>
       </c>
@@ -3997,7 +4075,7 @@
       </c>
       <c r="H169" s="8"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="5">
         <v>30651</v>
       </c>
@@ -4018,7 +4096,7 @@
       </c>
       <c r="H170" s="8"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="5">
         <v>30682</v>
       </c>
@@ -4039,7 +4117,7 @@
       </c>
       <c r="H171" s="8"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="5">
         <v>30713</v>
       </c>
@@ -4060,7 +4138,7 @@
       </c>
       <c r="H172" s="8"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="5">
         <v>30742</v>
       </c>
@@ -4081,7 +4159,7 @@
       </c>
       <c r="H173" s="8"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="5">
         <v>30773</v>
       </c>
@@ -4102,7 +4180,7 @@
       </c>
       <c r="H174" s="8"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="5">
         <v>30803</v>
       </c>
@@ -4123,7 +4201,7 @@
       </c>
       <c r="H175" s="8"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="5">
         <v>30834</v>
       </c>
@@ -4144,7 +4222,7 @@
       </c>
       <c r="H176" s="8"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="5">
         <v>30864</v>
       </c>
@@ -4165,7 +4243,7 @@
       </c>
       <c r="H177" s="8"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="5">
         <v>30895</v>
       </c>
@@ -4186,7 +4264,7 @@
       </c>
       <c r="H178" s="8"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="5">
         <v>30926</v>
       </c>
@@ -4207,7 +4285,7 @@
       </c>
       <c r="H179" s="8"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="5">
         <v>30956</v>
       </c>
@@ -4228,7 +4306,7 @@
       </c>
       <c r="H180" s="8"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="5">
         <v>30987</v>
       </c>
@@ -4249,7 +4327,7 @@
       </c>
       <c r="H181" s="8"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="5">
         <v>31017</v>
       </c>
@@ -4270,7 +4348,7 @@
       </c>
       <c r="H182" s="8"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>31048</v>
       </c>
@@ -4291,7 +4369,7 @@
       </c>
       <c r="H183" s="8"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="5">
         <v>31079</v>
       </c>
@@ -4312,7 +4390,7 @@
       </c>
       <c r="H184" s="8"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="5">
         <v>31107</v>
       </c>
@@ -4333,7 +4411,7 @@
       </c>
       <c r="H185" s="8"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="5">
         <v>31138</v>
       </c>
@@ -4354,7 +4432,7 @@
       </c>
       <c r="H186" s="8"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="5">
         <v>31168</v>
       </c>
@@ -4375,7 +4453,7 @@
       </c>
       <c r="H187" s="8"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="5">
         <v>31199</v>
       </c>
@@ -4396,7 +4474,7 @@
       </c>
       <c r="H188" s="8"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="5">
         <v>31229</v>
       </c>
@@ -4417,7 +4495,7 @@
       </c>
       <c r="H189" s="8"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="5">
         <v>31260</v>
       </c>
@@ -4438,7 +4516,7 @@
       </c>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="5">
         <v>31291</v>
       </c>
@@ -4459,7 +4537,7 @@
       </c>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="5">
         <v>31321</v>
       </c>
@@ -4480,7 +4558,7 @@
       </c>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="5">
         <v>31352</v>
       </c>
@@ -4501,7 +4579,7 @@
       </c>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="5">
         <v>31382</v>
       </c>
@@ -4522,7 +4600,7 @@
       </c>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="5">
         <v>31413</v>
       </c>
@@ -4543,7 +4621,7 @@
       </c>
       <c r="H195" s="8"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="5">
         <v>31444</v>
       </c>
@@ -4564,7 +4642,7 @@
       </c>
       <c r="H196" s="8"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="5">
         <v>31472</v>
       </c>
@@ -4585,7 +4663,7 @@
       </c>
       <c r="H197" s="8"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="5">
         <v>31503</v>
       </c>
@@ -4606,7 +4684,7 @@
       </c>
       <c r="H198" s="8"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="5">
         <v>31533</v>
       </c>
@@ -4627,7 +4705,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="5">
         <v>31564</v>
       </c>
@@ -4648,7 +4726,7 @@
       </c>
       <c r="H200" s="8"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="5">
         <v>31594</v>
       </c>
@@ -4669,7 +4747,7 @@
       </c>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="5">
         <v>31625</v>
       </c>
@@ -4690,7 +4768,7 @@
       </c>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="5">
         <v>31656</v>
       </c>
@@ -4711,7 +4789,7 @@
       </c>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="5">
         <v>31686</v>
       </c>
@@ -4732,7 +4810,7 @@
       </c>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="5">
         <v>31717</v>
       </c>
@@ -4753,7 +4831,7 @@
       </c>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="5">
         <v>31747</v>
       </c>
@@ -4774,7 +4852,7 @@
       </c>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="5">
         <v>31778</v>
       </c>
@@ -4795,7 +4873,7 @@
       </c>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="5">
         <v>31809</v>
       </c>
@@ -4816,7 +4894,7 @@
       </c>
       <c r="H208" s="8"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="5">
         <v>31837</v>
       </c>
@@ -4837,7 +4915,7 @@
       </c>
       <c r="H209" s="8"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="5">
         <v>31868</v>
       </c>
@@ -4858,7 +4936,7 @@
       </c>
       <c r="H210" s="8"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="5">
         <v>31898</v>
       </c>
@@ -4879,7 +4957,7 @@
       </c>
       <c r="H211" s="8"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="5">
         <v>31929</v>
       </c>
@@ -4900,7 +4978,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="5">
         <v>31959</v>
       </c>
@@ -4921,7 +4999,7 @@
       </c>
       <c r="H213" s="8"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="5">
         <v>31990</v>
       </c>
@@ -4942,7 +5020,7 @@
       </c>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="5">
         <v>32021</v>
       </c>
@@ -4963,7 +5041,7 @@
       </c>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="5">
         <v>32051</v>
       </c>
@@ -4984,7 +5062,7 @@
       </c>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="5">
         <v>32082</v>
       </c>
@@ -5005,7 +5083,7 @@
       </c>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="5">
         <v>32112</v>
       </c>
@@ -5026,7 +5104,7 @@
       </c>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="5">
         <v>32143</v>
       </c>
@@ -5047,7 +5125,7 @@
       </c>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="5">
         <v>32174</v>
       </c>
@@ -5068,7 +5146,7 @@
       </c>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="5">
         <v>32203</v>
       </c>
@@ -5089,7 +5167,7 @@
       </c>
       <c r="H221" s="8"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="5">
         <v>32234</v>
       </c>
@@ -5110,7 +5188,7 @@
       </c>
       <c r="H222" s="8"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="5">
         <v>32264</v>
       </c>
@@ -5131,7 +5209,7 @@
       </c>
       <c r="H223" s="8"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="5">
         <v>32295</v>
       </c>
@@ -5152,7 +5230,7 @@
       </c>
       <c r="H224" s="8"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="5">
         <v>32325</v>
       </c>
@@ -5173,7 +5251,7 @@
       </c>
       <c r="H225" s="8"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="5">
         <v>32356</v>
       </c>
@@ -5194,7 +5272,7 @@
       </c>
       <c r="H226" s="8"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="5">
         <v>32387</v>
       </c>
@@ -5215,7 +5293,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="5">
         <v>32417</v>
       </c>
@@ -5236,7 +5314,7 @@
       </c>
       <c r="H228" s="8"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="5">
         <v>32448</v>
       </c>
@@ -5257,7 +5335,7 @@
       </c>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="5">
         <v>32478</v>
       </c>
@@ -5278,7 +5356,7 @@
       </c>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="5">
         <v>32509</v>
       </c>
@@ -5299,7 +5377,7 @@
       </c>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="5">
         <v>32540</v>
       </c>
@@ -5320,7 +5398,7 @@
       </c>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="5">
         <v>32568</v>
       </c>
@@ -5341,7 +5419,7 @@
       </c>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="5">
         <v>32599</v>
       </c>
@@ -5362,7 +5440,7 @@
       </c>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="5">
         <v>32629</v>
       </c>
@@ -5383,7 +5461,7 @@
       </c>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="5">
         <v>32660</v>
       </c>
@@ -5404,7 +5482,7 @@
       </c>
       <c r="H236" s="8"/>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="5">
         <v>32690</v>
       </c>
@@ -5425,7 +5503,7 @@
       </c>
       <c r="H237" s="8"/>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="5">
         <v>32721</v>
       </c>
@@ -5446,7 +5524,7 @@
       </c>
       <c r="H238" s="8"/>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="5">
         <v>32752</v>
       </c>
@@ -5467,7 +5545,7 @@
       </c>
       <c r="H239" s="8"/>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="5">
         <v>32782</v>
       </c>
@@ -5488,7 +5566,7 @@
       </c>
       <c r="H240" s="8"/>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="5">
         <v>32813</v>
       </c>
@@ -5509,7 +5587,7 @@
       </c>
       <c r="H241" s="8"/>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="5">
         <v>32843</v>
       </c>
@@ -5530,7 +5608,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="5">
         <v>32874</v>
       </c>
@@ -5551,7 +5629,7 @@
       </c>
       <c r="H243" s="8"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="5">
         <v>32905</v>
       </c>
@@ -5572,7 +5650,7 @@
       </c>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="5">
         <v>32933</v>
       </c>
@@ -5593,7 +5671,7 @@
       </c>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="5">
         <v>32964</v>
       </c>
@@ -5614,7 +5692,7 @@
       </c>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="5">
         <v>32994</v>
       </c>
@@ -5635,7 +5713,7 @@
       </c>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="5">
         <v>33025</v>
       </c>
@@ -5656,7 +5734,7 @@
       </c>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="5">
         <v>33055</v>
       </c>
@@ -5677,7 +5755,7 @@
       </c>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="5">
         <v>33086</v>
       </c>
@@ -5698,7 +5776,7 @@
       </c>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="5">
         <v>33117</v>
       </c>
@@ -5719,7 +5797,7 @@
       </c>
       <c r="H251" s="8"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="5">
         <v>33147</v>
       </c>
@@ -5740,7 +5818,7 @@
       </c>
       <c r="H252" s="8"/>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="5">
         <v>33178</v>
       </c>
@@ -5761,7 +5839,7 @@
       </c>
       <c r="H253" s="8"/>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="5">
         <v>33208</v>
       </c>
@@ -5782,7 +5860,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="5">
         <v>33239</v>
       </c>
@@ -5803,7 +5881,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="5">
         <v>33270</v>
       </c>
@@ -5824,7 +5902,7 @@
       </c>
       <c r="H256" s="8"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="5">
         <v>33298</v>
       </c>
@@ -5845,7 +5923,7 @@
       </c>
       <c r="H257" s="8"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="5">
         <v>33329</v>
       </c>
@@ -5866,7 +5944,7 @@
       </c>
       <c r="H258" s="8"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="5">
         <v>33359</v>
       </c>
@@ -5887,7 +5965,7 @@
       </c>
       <c r="H259" s="8"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="5">
         <v>33390</v>
       </c>
@@ -5908,7 +5986,7 @@
       </c>
       <c r="H260" s="8"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="5">
         <v>33420</v>
       </c>
@@ -5929,7 +6007,7 @@
       </c>
       <c r="H261" s="8"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="5">
         <v>33451</v>
       </c>
@@ -5950,7 +6028,7 @@
       </c>
       <c r="H262" s="8"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="5">
         <v>33482</v>
       </c>
@@ -5971,7 +6049,7 @@
       </c>
       <c r="H263" s="8"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="5">
         <v>33512</v>
       </c>
@@ -5992,7 +6070,7 @@
       </c>
       <c r="H264" s="8"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="5">
         <v>33543</v>
       </c>
@@ -6013,7 +6091,7 @@
       </c>
       <c r="H265" s="8"/>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="5">
         <v>33573</v>
       </c>
@@ -6034,7 +6112,7 @@
       </c>
       <c r="H266" s="8"/>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="5">
         <v>33604</v>
       </c>
@@ -6055,7 +6133,7 @@
       </c>
       <c r="H267" s="8"/>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="5">
         <v>33635</v>
       </c>
@@ -6076,7 +6154,7 @@
       </c>
       <c r="H268" s="8"/>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="5">
         <v>33664</v>
       </c>
@@ -6097,7 +6175,7 @@
       </c>
       <c r="H269" s="8"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="5">
         <v>33695</v>
       </c>
@@ -6118,7 +6196,7 @@
       </c>
       <c r="H270" s="8"/>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="5">
         <v>33725</v>
       </c>
@@ -6139,7 +6217,7 @@
       </c>
       <c r="H271" s="8"/>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="5">
         <v>33756</v>
       </c>
@@ -6160,7 +6238,7 @@
       </c>
       <c r="H272" s="8"/>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="5">
         <v>33786</v>
       </c>
@@ -6181,7 +6259,7 @@
       </c>
       <c r="H273" s="8"/>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="5">
         <v>33817</v>
       </c>
@@ -6202,7 +6280,7 @@
       </c>
       <c r="H274" s="8"/>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="5">
         <v>33848</v>
       </c>
@@ -6223,7 +6301,7 @@
       </c>
       <c r="H275" s="8"/>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="5">
         <v>33878</v>
       </c>
@@ -6244,7 +6322,7 @@
       </c>
       <c r="H276" s="8"/>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="5">
         <v>33909</v>
       </c>
@@ -6265,7 +6343,7 @@
       </c>
       <c r="H277" s="8"/>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="5">
         <v>33939</v>
       </c>
@@ -6286,7 +6364,7 @@
       </c>
       <c r="H278" s="8"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="5">
         <v>33970</v>
       </c>
@@ -6307,7 +6385,7 @@
       </c>
       <c r="H279" s="8"/>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="5">
         <v>34001</v>
       </c>
@@ -6328,7 +6406,7 @@
       </c>
       <c r="H280" s="8"/>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="5">
         <v>34029</v>
       </c>
@@ -6349,7 +6427,7 @@
       </c>
       <c r="H281" s="8"/>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="5">
         <v>34060</v>
       </c>
@@ -6370,7 +6448,7 @@
       </c>
       <c r="H282" s="8"/>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="5">
         <v>34090</v>
       </c>
@@ -6391,7 +6469,7 @@
       </c>
       <c r="H283" s="8"/>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="5">
         <v>34121</v>
       </c>
@@ -6412,7 +6490,7 @@
       </c>
       <c r="H284" s="8"/>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="5">
         <v>34151</v>
       </c>
@@ -6433,7 +6511,7 @@
       </c>
       <c r="H285" s="8"/>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="5">
         <v>34182</v>
       </c>
@@ -6454,7 +6532,7 @@
       </c>
       <c r="H286" s="8"/>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="5">
         <v>34213</v>
       </c>
@@ -6475,7 +6553,7 @@
       </c>
       <c r="H287" s="8"/>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="5">
         <v>34243</v>
       </c>
@@ -6496,7 +6574,7 @@
       </c>
       <c r="H288" s="8"/>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="5">
         <v>34274</v>
       </c>
@@ -6517,7 +6595,7 @@
       </c>
       <c r="H289" s="8"/>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="5">
         <v>34304</v>
       </c>
@@ -6538,7 +6616,7 @@
       </c>
       <c r="H290" s="8"/>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="5">
         <v>34335</v>
       </c>
@@ -6559,7 +6637,7 @@
       </c>
       <c r="H291" s="8"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="5">
         <v>34366</v>
       </c>
@@ -6580,7 +6658,7 @@
       </c>
       <c r="H292" s="8"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="5">
         <v>34394</v>
       </c>
@@ -6601,7 +6679,7 @@
       </c>
       <c r="H293" s="8"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="5">
         <v>34425</v>
       </c>
@@ -6622,7 +6700,7 @@
       </c>
       <c r="H294" s="8"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="5">
         <v>34455</v>
       </c>
@@ -6643,7 +6721,7 @@
       </c>
       <c r="H295" s="8"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="5">
         <v>34486</v>
       </c>
@@ -6664,7 +6742,7 @@
       </c>
       <c r="H296" s="8"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="5">
         <v>34516</v>
       </c>
@@ -6685,7 +6763,7 @@
       </c>
       <c r="H297" s="8"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="5">
         <v>34547</v>
       </c>
@@ -6706,7 +6784,7 @@
       </c>
       <c r="H298" s="8"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="5">
         <v>34578</v>
       </c>
@@ -6727,7 +6805,7 @@
       </c>
       <c r="H299" s="8"/>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="5">
         <v>34608</v>
       </c>
@@ -6748,7 +6826,7 @@
       </c>
       <c r="H300" s="8"/>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="5">
         <v>34639</v>
       </c>
@@ -6769,7 +6847,7 @@
       </c>
       <c r="H301" s="8"/>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="5">
         <v>34669</v>
       </c>
@@ -6790,7 +6868,7 @@
       </c>
       <c r="H302" s="8"/>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="5">
         <v>34700</v>
       </c>
@@ -6811,7 +6889,7 @@
       </c>
       <c r="H303" s="8"/>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="5">
         <v>34731</v>
       </c>
@@ -6832,7 +6910,7 @@
       </c>
       <c r="H304" s="8"/>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="5">
         <v>34759</v>
       </c>
@@ -6853,7 +6931,7 @@
       </c>
       <c r="H305" s="8"/>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="5">
         <v>34790</v>
       </c>
@@ -6874,7 +6952,7 @@
       </c>
       <c r="H306" s="8"/>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="5">
         <v>34820</v>
       </c>
@@ -6895,7 +6973,7 @@
       </c>
       <c r="H307" s="8"/>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="5">
         <v>34851</v>
       </c>
@@ -6916,7 +6994,7 @@
       </c>
       <c r="H308" s="8"/>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="5">
         <v>34881</v>
       </c>
@@ -6937,7 +7015,7 @@
       </c>
       <c r="H309" s="8"/>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="5">
         <v>34912</v>
       </c>
@@ -6958,7 +7036,7 @@
       </c>
       <c r="H310" s="8"/>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="5">
         <v>34943</v>
       </c>
@@ -6979,7 +7057,7 @@
       </c>
       <c r="H311" s="8"/>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="5">
         <v>34973</v>
       </c>
@@ -7000,7 +7078,7 @@
       </c>
       <c r="H312" s="8"/>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="5">
         <v>35004</v>
       </c>
@@ -7021,7 +7099,7 @@
       </c>
       <c r="H313" s="8"/>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="5">
         <v>35034</v>
       </c>
@@ -7042,7 +7120,7 @@
       </c>
       <c r="H314" s="8"/>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="5">
         <v>35065</v>
       </c>
@@ -7063,7 +7141,7 @@
       </c>
       <c r="H315" s="8"/>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="5">
         <v>35096</v>
       </c>
@@ -7084,7 +7162,7 @@
       </c>
       <c r="H316" s="8"/>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="5">
         <v>35125</v>
       </c>
@@ -7105,7 +7183,7 @@
       </c>
       <c r="H317" s="8"/>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="5">
         <v>35156</v>
       </c>
@@ -7126,7 +7204,7 @@
       </c>
       <c r="H318" s="8"/>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="5">
         <v>35186</v>
       </c>
@@ -7147,7 +7225,7 @@
       </c>
       <c r="H319" s="8"/>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="5">
         <v>35217</v>
       </c>
@@ -7168,7 +7246,7 @@
       </c>
       <c r="H320" s="8"/>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="5">
         <v>35247</v>
       </c>
@@ -7189,7 +7267,7 @@
       </c>
       <c r="H321" s="8"/>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="5">
         <v>35278</v>
       </c>
@@ -7210,7 +7288,7 @@
       </c>
       <c r="H322" s="8"/>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="5">
         <v>35309</v>
       </c>
@@ -7231,7 +7309,7 @@
       </c>
       <c r="H323" s="8"/>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="5">
         <v>35339</v>
       </c>
@@ -7252,7 +7330,7 @@
       </c>
       <c r="H324" s="8"/>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="5">
         <v>35370</v>
       </c>
@@ -7273,7 +7351,7 @@
       </c>
       <c r="H325" s="8"/>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="5">
         <v>35400</v>
       </c>
@@ -7294,7 +7372,7 @@
       </c>
       <c r="H326" s="8"/>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="5">
         <v>35431</v>
       </c>
@@ -7315,7 +7393,7 @@
       </c>
       <c r="H327" s="8"/>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="5">
         <v>35462</v>
       </c>
@@ -7336,7 +7414,7 @@
       </c>
       <c r="H328" s="8"/>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="5">
         <v>35490</v>
       </c>
@@ -7357,7 +7435,7 @@
       </c>
       <c r="H329" s="8"/>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="5">
         <v>35521</v>
       </c>
@@ -7378,7 +7456,7 @@
       </c>
       <c r="H330" s="8"/>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="5">
         <v>35551</v>
       </c>
@@ -7399,7 +7477,7 @@
       </c>
       <c r="H331" s="8"/>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="5">
         <v>35582</v>
       </c>
@@ -7420,7 +7498,7 @@
       </c>
       <c r="H332" s="8"/>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="5">
         <v>35612</v>
       </c>
@@ -7441,7 +7519,7 @@
       </c>
       <c r="H333" s="8"/>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="5">
         <v>35643</v>
       </c>
@@ -7462,7 +7540,7 @@
       </c>
       <c r="H334" s="8"/>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="5">
         <v>35674</v>
       </c>
@@ -7483,7 +7561,7 @@
       </c>
       <c r="H335" s="8"/>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="5">
         <v>35704</v>
       </c>
@@ -7504,7 +7582,7 @@
       </c>
       <c r="H336" s="8"/>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="5">
         <v>35735</v>
       </c>
@@ -7525,7 +7603,7 @@
       </c>
       <c r="H337" s="8"/>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="5">
         <v>35765</v>
       </c>
@@ -7546,7 +7624,7 @@
       </c>
       <c r="H338" s="8"/>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="5">
         <v>35796</v>
       </c>
@@ -7567,7 +7645,7 @@
       </c>
       <c r="H339" s="8"/>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="5">
         <v>35827</v>
       </c>
@@ -7588,7 +7666,7 @@
       </c>
       <c r="H340" s="8"/>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="5">
         <v>35855</v>
       </c>
@@ -7609,7 +7687,7 @@
       </c>
       <c r="H341" s="8"/>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="5">
         <v>35886</v>
       </c>
@@ -7630,7 +7708,7 @@
       </c>
       <c r="H342" s="8"/>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="5">
         <v>35916</v>
       </c>
@@ -7651,7 +7729,7 @@
       </c>
       <c r="H343" s="8"/>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="5">
         <v>35947</v>
       </c>
@@ -7672,7 +7750,7 @@
       </c>
       <c r="H344" s="8"/>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="5">
         <v>35977</v>
       </c>
@@ -7693,7 +7771,7 @@
       </c>
       <c r="H345" s="8"/>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="5">
         <v>36008</v>
       </c>
@@ -7714,7 +7792,7 @@
       </c>
       <c r="H346" s="8"/>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="5">
         <v>36039</v>
       </c>
@@ -7735,7 +7813,7 @@
       </c>
       <c r="H347" s="8"/>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="5">
         <v>36069</v>
       </c>
@@ -7756,7 +7834,7 @@
       </c>
       <c r="H348" s="8"/>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="5">
         <v>36100</v>
       </c>
@@ -7777,7 +7855,7 @@
       </c>
       <c r="H349" s="8"/>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="5">
         <v>36130</v>
       </c>
@@ -7798,7 +7876,7 @@
       </c>
       <c r="H350" s="8"/>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="5">
         <v>36161</v>
       </c>
@@ -7819,7 +7897,7 @@
       </c>
       <c r="H351" s="8"/>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="5">
         <v>36192</v>
       </c>
@@ -7840,7 +7918,7 @@
       </c>
       <c r="H352" s="8"/>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="5">
         <v>36220</v>
       </c>
@@ -7861,7 +7939,7 @@
       </c>
       <c r="H353" s="8"/>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="5">
         <v>36251</v>
       </c>
@@ -7882,7 +7960,7 @@
       </c>
       <c r="H354" s="8"/>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="5">
         <v>36281</v>
       </c>
@@ -7903,7 +7981,7 @@
       </c>
       <c r="H355" s="8"/>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="5">
         <v>36312</v>
       </c>
@@ -7924,7 +8002,7 @@
       </c>
       <c r="H356" s="8"/>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="5">
         <v>36342</v>
       </c>
@@ -7945,7 +8023,7 @@
       </c>
       <c r="H357" s="8"/>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="5">
         <v>36373</v>
       </c>
@@ -7966,7 +8044,7 @@
       </c>
       <c r="H358" s="8"/>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="5">
         <v>36404</v>
       </c>
@@ -7987,7 +8065,7 @@
       </c>
       <c r="H359" s="8"/>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="5">
         <v>36434</v>
       </c>
@@ -8008,7 +8086,7 @@
       </c>
       <c r="H360" s="8"/>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="5">
         <v>36465</v>
       </c>
@@ -8029,7 +8107,7 @@
       </c>
       <c r="H361" s="8"/>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="5">
         <v>36495</v>
       </c>
@@ -8050,7 +8128,7 @@
       </c>
       <c r="H362" s="8"/>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="5">
         <v>36526</v>
       </c>
@@ -8071,7 +8149,7 @@
       </c>
       <c r="H363" s="8"/>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="5">
         <v>36557</v>
       </c>
@@ -8092,7 +8170,7 @@
       </c>
       <c r="H364" s="8"/>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="5">
         <v>36586</v>
       </c>
@@ -8113,7 +8191,7 @@
       </c>
       <c r="H365" s="8"/>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="5">
         <v>36617</v>
       </c>
@@ -8134,7 +8212,7 @@
       </c>
       <c r="H366" s="8"/>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="5">
         <v>36647</v>
       </c>
@@ -8155,7 +8233,7 @@
       </c>
       <c r="H367" s="8"/>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="5">
         <v>36678</v>
       </c>
@@ -8176,7 +8254,7 @@
       </c>
       <c r="H368" s="8"/>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="5">
         <v>36708</v>
       </c>
@@ -8197,7 +8275,7 @@
       </c>
       <c r="H369" s="8"/>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="5">
         <v>36739</v>
       </c>
@@ -8218,7 +8296,7 @@
       </c>
       <c r="H370" s="8"/>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="5">
         <v>36770</v>
       </c>
@@ -8239,7 +8317,7 @@
       </c>
       <c r="H371" s="8"/>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="5">
         <v>36800</v>
       </c>
@@ -8260,7 +8338,7 @@
       </c>
       <c r="H372" s="8"/>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="5">
         <v>36831</v>
       </c>
@@ -8281,7 +8359,7 @@
       </c>
       <c r="H373" s="8"/>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="5">
         <v>36861</v>
       </c>
@@ -8302,7 +8380,7 @@
       </c>
       <c r="H374" s="8"/>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="5">
         <v>36892</v>
       </c>
@@ -8323,7 +8401,7 @@
       </c>
       <c r="H375" s="8"/>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="5">
         <v>36923</v>
       </c>
@@ -8344,7 +8422,7 @@
       </c>
       <c r="H376" s="8"/>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="5">
         <v>36951</v>
       </c>
@@ -8365,7 +8443,7 @@
       </c>
       <c r="H377" s="8"/>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="5">
         <v>36982</v>
       </c>
@@ -8386,7 +8464,7 @@
       </c>
       <c r="H378" s="8"/>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="5">
         <v>37012</v>
       </c>
@@ -8407,7 +8485,7 @@
       </c>
       <c r="H379" s="8"/>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="5">
         <v>37043</v>
       </c>
@@ -8428,7 +8506,7 @@
       </c>
       <c r="H380" s="8"/>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="5">
         <v>37073</v>
       </c>
@@ -8449,7 +8527,7 @@
       </c>
       <c r="H381" s="8"/>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="5">
         <v>37104</v>
       </c>
@@ -8470,7 +8548,7 @@
       </c>
       <c r="H382" s="8"/>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="5">
         <v>37135</v>
       </c>
@@ -8491,7 +8569,7 @@
       </c>
       <c r="H383" s="8"/>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="5">
         <v>37165</v>
       </c>
@@ -8512,7 +8590,7 @@
       </c>
       <c r="H384" s="8"/>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="5">
         <v>37196</v>
       </c>
@@ -8533,7 +8611,7 @@
       </c>
       <c r="H385" s="8"/>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="5">
         <v>37226</v>
       </c>
@@ -8554,7 +8632,7 @@
       </c>
       <c r="H386" s="8"/>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="5">
         <v>37257</v>
       </c>
@@ -8575,7 +8653,7 @@
       </c>
       <c r="H387" s="8"/>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="5">
         <v>37288</v>
       </c>
@@ -8596,7 +8674,7 @@
       </c>
       <c r="H388" s="8"/>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="5">
         <v>37316</v>
       </c>
@@ -8617,7 +8695,7 @@
       </c>
       <c r="H389" s="8"/>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="5">
         <v>37347</v>
       </c>
@@ -8638,7 +8716,7 @@
       </c>
       <c r="H390" s="8"/>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="5">
         <v>37377</v>
       </c>
@@ -8659,7 +8737,7 @@
       </c>
       <c r="H391" s="8"/>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="5">
         <v>37408</v>
       </c>
@@ -8680,7 +8758,7 @@
       </c>
       <c r="H392" s="8"/>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="5">
         <v>37438</v>
       </c>
@@ -8701,7 +8779,7 @@
       </c>
       <c r="H393" s="8"/>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="5">
         <v>37469</v>
       </c>
@@ -8722,7 +8800,7 @@
       </c>
       <c r="H394" s="8"/>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="5">
         <v>37500</v>
       </c>
@@ -8743,7 +8821,7 @@
       </c>
       <c r="H395" s="8"/>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="5">
         <v>37530</v>
       </c>
@@ -8764,7 +8842,7 @@
       </c>
       <c r="H396" s="8"/>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="5">
         <v>37561</v>
       </c>
@@ -8785,7 +8863,7 @@
       </c>
       <c r="H397" s="8"/>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="5">
         <v>37591</v>
       </c>
@@ -8806,7 +8884,7 @@
       </c>
       <c r="H398" s="8"/>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="5">
         <v>37622</v>
       </c>
@@ -8827,7 +8905,7 @@
       </c>
       <c r="H399" s="8"/>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="5">
         <v>37653</v>
       </c>
@@ -8848,7 +8926,7 @@
       </c>
       <c r="H400" s="8"/>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="5">
         <v>37681</v>
       </c>
@@ -8869,7 +8947,7 @@
       </c>
       <c r="H401" s="8"/>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="5">
         <v>37712</v>
       </c>
@@ -8890,7 +8968,7 @@
       </c>
       <c r="H402" s="8"/>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="5">
         <v>37742</v>
       </c>
@@ -8911,7 +8989,7 @@
       </c>
       <c r="H403" s="8"/>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="5">
         <v>37773</v>
       </c>
@@ -8932,7 +9010,7 @@
       </c>
       <c r="H404" s="8"/>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="5">
         <v>37803</v>
       </c>
@@ -8953,7 +9031,7 @@
       </c>
       <c r="H405" s="8"/>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="5">
         <v>37834</v>
       </c>
@@ -8974,7 +9052,7 @@
       </c>
       <c r="H406" s="8"/>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="5">
         <v>37865</v>
       </c>
@@ -8995,7 +9073,7 @@
       </c>
       <c r="H407" s="8"/>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="5">
         <v>37895</v>
       </c>
@@ -9016,7 +9094,7 @@
       </c>
       <c r="H408" s="8"/>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="5">
         <v>37926</v>
       </c>
@@ -9037,7 +9115,7 @@
       </c>
       <c r="H409" s="8"/>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="5">
         <v>37956</v>
       </c>
@@ -9058,7 +9136,7 @@
       </c>
       <c r="H410" s="8"/>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="5">
         <v>37987</v>
       </c>
@@ -9079,7 +9157,7 @@
       </c>
       <c r="H411" s="8"/>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" s="5">
         <v>38018</v>
       </c>
@@ -9100,7 +9178,7 @@
       </c>
       <c r="H412" s="8"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" s="5">
         <v>38047</v>
       </c>
@@ -9121,7 +9199,7 @@
       </c>
       <c r="H413" s="8"/>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="5">
         <v>38078</v>
       </c>
@@ -9142,7 +9220,7 @@
       </c>
       <c r="H414" s="8"/>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="5">
         <v>38108</v>
       </c>
@@ -9163,7 +9241,7 @@
       </c>
       <c r="H415" s="8"/>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="5">
         <v>38139</v>
       </c>
@@ -9184,7 +9262,7 @@
       </c>
       <c r="H416" s="8"/>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="5">
         <v>38169</v>
       </c>
@@ -9205,7 +9283,7 @@
       </c>
       <c r="H417" s="8"/>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="5">
         <v>38200</v>
       </c>
@@ -9226,7 +9304,7 @@
       </c>
       <c r="H418" s="8"/>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="5">
         <v>38231</v>
       </c>
@@ -9247,7 +9325,7 @@
       </c>
       <c r="H419" s="8"/>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="5">
         <v>38261</v>
       </c>
@@ -9268,7 +9346,7 @@
       </c>
       <c r="H420" s="8"/>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="5">
         <v>38292</v>
       </c>
@@ -9289,7 +9367,7 @@
       </c>
       <c r="H421" s="8"/>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="5">
         <v>38322</v>
       </c>
@@ -9310,7 +9388,7 @@
       </c>
       <c r="H422" s="8"/>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="5">
         <v>38353</v>
       </c>
@@ -9331,7 +9409,7 @@
       </c>
       <c r="H423" s="8"/>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="5">
         <v>38384</v>
       </c>
@@ -9352,7 +9430,7 @@
       </c>
       <c r="H424" s="8"/>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="5">
         <v>38412</v>
       </c>
@@ -9373,7 +9451,7 @@
       </c>
       <c r="H425" s="8"/>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="5">
         <v>38443</v>
       </c>
@@ -9394,7 +9472,7 @@
       </c>
       <c r="H426" s="8"/>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="5">
         <v>38473</v>
       </c>
@@ -9415,7 +9493,7 @@
       </c>
       <c r="H427" s="8"/>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="5">
         <v>38504</v>
       </c>
@@ -9436,7 +9514,7 @@
       </c>
       <c r="H428" s="8"/>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="5">
         <v>38534</v>
       </c>
@@ -9457,7 +9535,7 @@
       </c>
       <c r="H429" s="8"/>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="5">
         <v>38565</v>
       </c>
@@ -9478,7 +9556,7 @@
       </c>
       <c r="H430" s="8"/>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="5">
         <v>38596</v>
       </c>
@@ -9499,7 +9577,7 @@
       </c>
       <c r="H431" s="8"/>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="5">
         <v>38626</v>
       </c>
@@ -9520,7 +9598,7 @@
       </c>
       <c r="H432" s="8"/>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" s="5">
         <v>38657</v>
       </c>
@@ -9541,7 +9619,7 @@
       </c>
       <c r="H433" s="8"/>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" s="5">
         <v>38687</v>
       </c>
@@ -9562,7 +9640,7 @@
       </c>
       <c r="H434" s="8"/>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" s="5">
         <v>38718</v>
       </c>
@@ -9583,7 +9661,7 @@
       </c>
       <c r="H435" s="8"/>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" s="5">
         <v>38749</v>
       </c>
@@ -9604,7 +9682,7 @@
       </c>
       <c r="H436" s="8"/>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" s="5">
         <v>38777</v>
       </c>
@@ -9625,7 +9703,7 @@
       </c>
       <c r="H437" s="8"/>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="5">
         <v>38808</v>
       </c>
@@ -9646,7 +9724,7 @@
       </c>
       <c r="H438" s="8"/>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" s="5">
         <v>38838</v>
       </c>
@@ -9667,7 +9745,7 @@
       </c>
       <c r="H439" s="8"/>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="5">
         <v>38869</v>
       </c>
@@ -9688,7 +9766,7 @@
       </c>
       <c r="H440" s="8"/>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="5">
         <v>38899</v>
       </c>
@@ -9709,7 +9787,7 @@
       </c>
       <c r="H441" s="8"/>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" s="5">
         <v>38930</v>
       </c>
@@ -9730,7 +9808,7 @@
       </c>
       <c r="H442" s="8"/>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" s="5">
         <v>38961</v>
       </c>
@@ -9751,7 +9829,7 @@
       </c>
       <c r="H443" s="8"/>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" s="5">
         <v>38991</v>
       </c>
@@ -9772,7 +9850,7 @@
       </c>
       <c r="H444" s="8"/>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" s="5">
         <v>39022</v>
       </c>
@@ -9793,7 +9871,7 @@
       </c>
       <c r="H445" s="8"/>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" s="5">
         <v>39052</v>
       </c>
@@ -9814,7 +9892,7 @@
       </c>
       <c r="H446" s="8"/>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" s="5">
         <v>39083</v>
       </c>
@@ -9835,7 +9913,7 @@
       </c>
       <c r="H447" s="8"/>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" s="5">
         <v>39114</v>
       </c>
@@ -9856,7 +9934,7 @@
       </c>
       <c r="H448" s="8"/>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" s="5">
         <v>39142</v>
       </c>
@@ -9877,7 +9955,7 @@
       </c>
       <c r="H449" s="8"/>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" s="5">
         <v>39173</v>
       </c>
@@ -9898,7 +9976,7 @@
       </c>
       <c r="H450" s="8"/>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" s="5">
         <v>39203</v>
       </c>
@@ -9919,7 +9997,7 @@
       </c>
       <c r="H451" s="8"/>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" s="5">
         <v>39234</v>
       </c>
@@ -9940,7 +10018,7 @@
       </c>
       <c r="H452" s="8"/>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" s="5">
         <v>39264</v>
       </c>
@@ -9961,7 +10039,7 @@
       </c>
       <c r="H453" s="8"/>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" s="5">
         <v>39295</v>
       </c>
@@ -9982,7 +10060,7 @@
       </c>
       <c r="H454" s="8"/>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" s="5">
         <v>39326</v>
       </c>
@@ -10003,7 +10081,7 @@
       </c>
       <c r="H455" s="8"/>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" s="5">
         <v>39356</v>
       </c>
@@ -10024,7 +10102,7 @@
       </c>
       <c r="H456" s="8"/>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" s="5">
         <v>39387</v>
       </c>
@@ -10045,7 +10123,7 @@
       </c>
       <c r="H457" s="8"/>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" s="5">
         <v>39417</v>
       </c>
@@ -10066,7 +10144,7 @@
       </c>
       <c r="H458" s="8"/>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" s="5">
         <v>39448</v>
       </c>
@@ -10087,7 +10165,7 @@
       </c>
       <c r="H459" s="8"/>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" s="5">
         <v>39479</v>
       </c>
@@ -10108,7 +10186,7 @@
       </c>
       <c r="H460" s="8"/>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" s="5">
         <v>39508</v>
       </c>
@@ -10129,7 +10207,7 @@
       </c>
       <c r="H461" s="8"/>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" s="5">
         <v>39539</v>
       </c>
@@ -10150,7 +10228,7 @@
       </c>
       <c r="H462" s="8"/>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" s="5">
         <v>39569</v>
       </c>
@@ -10171,7 +10249,7 @@
       </c>
       <c r="H463" s="8"/>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" s="5">
         <v>39600</v>
       </c>
@@ -10192,7 +10270,7 @@
       </c>
       <c r="H464" s="8"/>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" s="5">
         <v>39630</v>
       </c>
@@ -10213,7 +10291,7 @@
       </c>
       <c r="H465" s="8"/>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="5">
         <v>39661</v>
       </c>
@@ -10234,7 +10312,7 @@
       </c>
       <c r="H466" s="8"/>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" s="5">
         <v>39692</v>
       </c>
@@ -10255,7 +10333,7 @@
       </c>
       <c r="H467" s="8"/>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="5">
         <v>39722</v>
       </c>
@@ -10276,7 +10354,7 @@
       </c>
       <c r="H468" s="8"/>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" s="5">
         <v>39753</v>
       </c>
@@ -10297,7 +10375,7 @@
       </c>
       <c r="H469" s="8"/>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" s="5">
         <v>39783</v>
       </c>
@@ -10318,7 +10396,7 @@
       </c>
       <c r="H470" s="8"/>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" s="5">
         <v>39814</v>
       </c>
@@ -10339,7 +10417,7 @@
       </c>
       <c r="H471" s="8"/>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="5">
         <v>39845</v>
       </c>
@@ -10360,7 +10438,7 @@
       </c>
       <c r="H472" s="8"/>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="5">
         <v>39873</v>
       </c>
@@ -10381,7 +10459,7 @@
       </c>
       <c r="H473" s="8"/>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="5">
         <v>39904</v>
       </c>
@@ -10402,7 +10480,7 @@
       </c>
       <c r="H474" s="8"/>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="5">
         <v>39934</v>
       </c>
@@ -10423,7 +10501,7 @@
       </c>
       <c r="H475" s="8"/>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="5">
         <v>39965</v>
       </c>
@@ -10444,7 +10522,7 @@
       </c>
       <c r="H476" s="8"/>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="5">
         <v>39995</v>
       </c>
@@ -10465,7 +10543,7 @@
       </c>
       <c r="H477" s="8"/>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" s="5">
         <v>40026</v>
       </c>
@@ -10486,7 +10564,7 @@
       </c>
       <c r="H478" s="8"/>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" s="5">
         <v>40057</v>
       </c>
@@ -10507,7 +10585,7 @@
       </c>
       <c r="H479" s="8"/>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" s="5">
         <v>40087</v>
       </c>
@@ -10528,7 +10606,7 @@
       </c>
       <c r="H480" s="8"/>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" s="5">
         <v>40118</v>
       </c>
@@ -10549,7 +10627,7 @@
       </c>
       <c r="H481" s="8"/>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="5">
         <v>40148</v>
       </c>
@@ -10570,7 +10648,7 @@
       </c>
       <c r="H482" s="8"/>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" s="5">
         <v>40179</v>
       </c>
@@ -10591,7 +10669,7 @@
       </c>
       <c r="H483" s="8"/>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" s="5">
         <v>40210</v>
       </c>
@@ -10612,7 +10690,7 @@
       </c>
       <c r="H484" s="8"/>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" s="5">
         <v>40238</v>
       </c>
@@ -10633,7 +10711,7 @@
       </c>
       <c r="H485" s="8"/>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" s="5">
         <v>40269</v>
       </c>
@@ -10654,7 +10732,7 @@
       </c>
       <c r="H486" s="8"/>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" s="5">
         <v>40299</v>
       </c>
@@ -10675,7 +10753,7 @@
       </c>
       <c r="H487" s="8"/>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" s="5">
         <v>40330</v>
       </c>
@@ -10696,7 +10774,7 @@
       </c>
       <c r="H488" s="8"/>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" s="5">
         <v>40360</v>
       </c>
@@ -10717,7 +10795,7 @@
       </c>
       <c r="H489" s="8"/>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A490" s="5">
         <v>40391</v>
       </c>
@@ -10738,7 +10816,7 @@
       </c>
       <c r="H490" s="8"/>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" s="5">
         <v>40422</v>
       </c>
@@ -10759,7 +10837,7 @@
       </c>
       <c r="H491" s="8"/>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" s="5">
         <v>40452</v>
       </c>
@@ -10780,7 +10858,7 @@
       </c>
       <c r="H492" s="8"/>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" s="5">
         <v>40483</v>
       </c>
@@ -10801,7 +10879,7 @@
       </c>
       <c r="H493" s="8"/>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" s="5">
         <v>40513</v>
       </c>
@@ -10825,7 +10903,7 @@
       </c>
       <c r="H494" s="8"/>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" s="5">
         <v>40544</v>
       </c>
@@ -10849,7 +10927,7 @@
       </c>
       <c r="H495" s="8"/>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" s="5">
         <v>40575</v>
       </c>
@@ -10873,7 +10951,7 @@
       </c>
       <c r="H496" s="8"/>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" s="5">
         <v>40603</v>
       </c>
@@ -10897,7 +10975,7 @@
       </c>
       <c r="H497" s="8"/>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" s="5">
         <v>40634</v>
       </c>
@@ -10921,7 +10999,7 @@
       </c>
       <c r="H498" s="8"/>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A499" s="5">
         <v>40664</v>
       </c>
@@ -10945,7 +11023,7 @@
       </c>
       <c r="H499" s="8"/>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A500" s="5">
         <v>40695</v>
       </c>
@@ -10969,7 +11047,7 @@
       </c>
       <c r="H500" s="8"/>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A501" s="5">
         <v>40725</v>
       </c>
@@ -10993,7 +11071,7 @@
       </c>
       <c r="H501" s="8"/>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A502" s="5">
         <v>40756</v>
       </c>
@@ -11017,7 +11095,7 @@
       </c>
       <c r="H502" s="8"/>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A503" s="5">
         <v>40787</v>
       </c>
@@ -11041,7 +11119,7 @@
       </c>
       <c r="H503" s="8"/>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A504" s="5">
         <v>40817</v>
       </c>
@@ -11065,7 +11143,7 @@
       </c>
       <c r="H504" s="8"/>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A505" s="5">
         <v>40848</v>
       </c>
@@ -11089,7 +11167,7 @@
       </c>
       <c r="H505" s="8"/>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A506" s="5">
         <v>40878</v>
       </c>
@@ -11113,7 +11191,7 @@
       </c>
       <c r="H506" s="8"/>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A507" s="5">
         <v>40909</v>
       </c>
@@ -11137,7 +11215,7 @@
       </c>
       <c r="H507" s="8"/>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A508" s="5">
         <v>40940</v>
       </c>
@@ -11161,7 +11239,7 @@
       </c>
       <c r="H508" s="8"/>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A509" s="5">
         <v>40969</v>
       </c>
@@ -11185,7 +11263,7 @@
       </c>
       <c r="H509" s="8"/>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A510" s="5">
         <v>41000</v>
       </c>
@@ -11209,7 +11287,7 @@
       </c>
       <c r="H510" s="8"/>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A511" s="5">
         <v>41030</v>
       </c>
@@ -11233,7 +11311,7 @@
       </c>
       <c r="H511" s="8"/>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A512" s="5">
         <v>41061</v>
       </c>
@@ -11257,7 +11335,7 @@
       </c>
       <c r="H512" s="8"/>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A513" s="5">
         <v>41091</v>
       </c>
@@ -11281,7 +11359,7 @@
       </c>
       <c r="H513" s="8"/>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A514" s="5">
         <v>41122</v>
       </c>
@@ -11305,7 +11383,7 @@
       </c>
       <c r="H514" s="8"/>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A515" s="5">
         <v>41153</v>
       </c>
@@ -11329,7 +11407,7 @@
       </c>
       <c r="H515" s="8"/>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A516" s="5">
         <v>41183</v>
       </c>
@@ -11353,7 +11431,7 @@
       </c>
       <c r="H516" s="8"/>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A517" s="5">
         <v>41214</v>
       </c>
@@ -11377,7 +11455,7 @@
       </c>
       <c r="H517" s="8"/>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A518" s="5">
         <v>41244</v>
       </c>
@@ -11401,7 +11479,7 @@
       </c>
       <c r="H518" s="8"/>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A519" s="5">
         <v>41275</v>
       </c>
@@ -11425,7 +11503,7 @@
       </c>
       <c r="H519" s="8"/>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A520" s="5">
         <v>41306</v>
       </c>
@@ -11449,7 +11527,7 @@
       </c>
       <c r="H520" s="8"/>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A521" s="5">
         <v>41334</v>
       </c>
@@ -11473,7 +11551,7 @@
       </c>
       <c r="H521" s="8"/>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A522" s="5">
         <v>41365</v>
       </c>
@@ -11497,7 +11575,7 @@
       </c>
       <c r="H522" s="8"/>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A523" s="5">
         <v>41395</v>
       </c>
@@ -11521,7 +11599,7 @@
       </c>
       <c r="H523" s="8"/>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A524" s="5">
         <v>41426</v>
       </c>
@@ -11545,7 +11623,7 @@
       </c>
       <c r="H524" s="8"/>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A525" s="5">
         <v>41456</v>
       </c>
@@ -11569,7 +11647,7 @@
       </c>
       <c r="H525" s="8"/>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A526" s="5">
         <v>41487</v>
       </c>
@@ -11593,7 +11671,7 @@
       </c>
       <c r="H526" s="8"/>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A527" s="5">
         <v>41518</v>
       </c>
@@ -11617,7 +11695,7 @@
       </c>
       <c r="H527" s="8"/>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A528" s="5">
         <v>41548</v>
       </c>
@@ -11641,7 +11719,7 @@
       </c>
       <c r="H528" s="8"/>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A529" s="5">
         <v>41579</v>
       </c>
@@ -11665,7 +11743,7 @@
       </c>
       <c r="H529" s="8"/>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A530" s="5">
         <v>41609</v>
       </c>
@@ -11689,7 +11767,7 @@
       </c>
       <c r="H530" s="8"/>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A531" s="5">
         <v>41640</v>
       </c>
@@ -11713,7 +11791,7 @@
       </c>
       <c r="H531" s="8"/>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A532" s="5">
         <v>41671</v>
       </c>
@@ -11737,7 +11815,7 @@
       </c>
       <c r="H532" s="8"/>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A533" s="5">
         <v>41699</v>
       </c>
@@ -11761,7 +11839,7 @@
       </c>
       <c r="H533" s="8"/>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A534" s="5">
         <v>41730</v>
       </c>
@@ -11785,7 +11863,7 @@
       </c>
       <c r="H534" s="8"/>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A535" s="5">
         <v>41760</v>
       </c>
@@ -11809,7 +11887,7 @@
       </c>
       <c r="H535" s="8"/>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A536" s="5">
         <v>41791</v>
       </c>
@@ -11833,7 +11911,7 @@
       </c>
       <c r="H536" s="8"/>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A537" s="5">
         <v>41821</v>
       </c>
@@ -11857,7 +11935,7 @@
       </c>
       <c r="H537" s="8"/>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A538" s="5">
         <v>41852</v>
       </c>
@@ -11881,7 +11959,7 @@
       </c>
       <c r="H538" s="8"/>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A539" s="5">
         <v>41883</v>
       </c>
@@ -11905,7 +11983,7 @@
       </c>
       <c r="H539" s="8"/>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A540" s="5">
         <v>41913</v>
       </c>
@@ -11929,7 +12007,7 @@
       </c>
       <c r="H540" s="8"/>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A541" s="5">
         <v>41944</v>
       </c>
@@ -11953,7 +12031,7 @@
       </c>
       <c r="H541" s="8"/>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A542" s="5">
         <v>41974</v>
       </c>
@@ -11977,7 +12055,7 @@
       </c>
       <c r="H542" s="8"/>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A543" s="5">
         <v>42005</v>
       </c>
@@ -12001,7 +12079,7 @@
       </c>
       <c r="H543" s="8"/>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A544" s="5">
         <v>42036</v>
       </c>
@@ -12025,7 +12103,7 @@
       </c>
       <c r="H544" s="8"/>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A545" s="5">
         <v>42064</v>
       </c>
@@ -12049,7 +12127,7 @@
       </c>
       <c r="H545" s="8"/>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A546" s="5">
         <v>42095</v>
       </c>
@@ -12073,7 +12151,7 @@
       </c>
       <c r="H546" s="8"/>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A547" s="5">
         <v>42125</v>
       </c>
@@ -12097,7 +12175,7 @@
       </c>
       <c r="H547" s="8"/>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A548" s="5">
         <v>42156</v>
       </c>
@@ -12121,7 +12199,7 @@
       </c>
       <c r="H548" s="8"/>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A549" s="5">
         <v>42186</v>
       </c>
@@ -12145,7 +12223,7 @@
       </c>
       <c r="H549" s="8"/>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A550" s="5">
         <v>42217</v>
       </c>
@@ -12169,7 +12247,7 @@
       </c>
       <c r="H550" s="8"/>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A551" s="5">
         <v>42248</v>
       </c>
@@ -12193,7 +12271,7 @@
       </c>
       <c r="H551" s="8"/>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A552" s="5">
         <v>42278</v>
       </c>
@@ -12217,7 +12295,7 @@
       </c>
       <c r="H552" s="8"/>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A553" s="5">
         <v>42309</v>
       </c>
@@ -12241,7 +12319,7 @@
       </c>
       <c r="H553" s="8"/>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A554" s="5">
         <v>42339</v>
       </c>
@@ -12265,7 +12343,7 @@
       </c>
       <c r="H554" s="8"/>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A555" s="5">
         <v>42370</v>
       </c>
@@ -12289,7 +12367,7 @@
       </c>
       <c r="H555" s="8"/>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A556" s="5">
         <v>42401</v>
       </c>
@@ -12313,7 +12391,7 @@
       </c>
       <c r="H556" s="8"/>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A557" s="5">
         <v>42430</v>
       </c>
@@ -12337,7 +12415,7 @@
       </c>
       <c r="H557" s="8"/>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A558" s="5">
         <v>42461</v>
       </c>
@@ -12361,7 +12439,7 @@
       </c>
       <c r="H558" s="8"/>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A559" s="5">
         <v>42491</v>
       </c>
@@ -12385,7 +12463,7 @@
       </c>
       <c r="H559" s="8"/>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A560" s="5">
         <v>42522</v>
       </c>
@@ -12409,7 +12487,7 @@
       </c>
       <c r="H560" s="8"/>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A561" s="5">
         <v>42552</v>
       </c>
@@ -12433,7 +12511,7 @@
       </c>
       <c r="H561" s="8"/>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A562" s="5">
         <v>42583</v>
       </c>
@@ -12457,7 +12535,7 @@
       </c>
       <c r="H562" s="8"/>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A563" s="5">
         <v>42614</v>
       </c>
@@ -12481,7 +12559,7 @@
       </c>
       <c r="H563" s="8"/>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A564" s="5">
         <v>42644</v>
       </c>
@@ -12505,7 +12583,7 @@
       </c>
       <c r="H564" s="8"/>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A565" s="5">
         <v>42675</v>
       </c>
@@ -12529,7 +12607,7 @@
       </c>
       <c r="H565" s="8"/>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A566" s="5">
         <v>42705</v>
       </c>
@@ -12553,7 +12631,7 @@
       </c>
       <c r="H566" s="8"/>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A567" s="5">
         <v>42736</v>
       </c>
@@ -12577,7 +12655,7 @@
       </c>
       <c r="H567" s="8"/>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A568" s="5">
         <v>42767</v>
       </c>
@@ -12601,7 +12679,7 @@
       </c>
       <c r="H568" s="8"/>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A569" s="5">
         <v>42795</v>
       </c>
@@ -12625,7 +12703,7 @@
       </c>
       <c r="H569" s="8"/>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A570" s="5">
         <v>42826</v>
       </c>
@@ -12649,7 +12727,7 @@
       </c>
       <c r="H570" s="8"/>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A571" s="5">
         <v>42856</v>
       </c>
@@ -12673,7 +12751,7 @@
       </c>
       <c r="H571" s="8"/>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A572" s="5">
         <v>42887</v>
       </c>
@@ -12697,7 +12775,7 @@
       </c>
       <c r="H572" s="8"/>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A573" s="5">
         <v>42917</v>
       </c>
@@ -12721,7 +12799,7 @@
       </c>
       <c r="H573" s="8"/>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A574" s="5">
         <v>42948</v>
       </c>
@@ -12745,7 +12823,7 @@
       </c>
       <c r="H574" s="8"/>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A575" s="5">
         <v>42979</v>
       </c>
@@ -12769,7 +12847,7 @@
       </c>
       <c r="H575" s="8"/>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A576" s="5">
         <v>43009</v>
       </c>
@@ -12793,7 +12871,7 @@
       </c>
       <c r="H576" s="8"/>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A577" s="5">
         <v>43040</v>
       </c>
@@ -12817,7 +12895,7 @@
       </c>
       <c r="H577" s="8"/>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A578" s="5">
         <v>43070</v>
       </c>
@@ -12841,7 +12919,7 @@
       </c>
       <c r="H578" s="8"/>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A579" s="5">
         <v>43101</v>
       </c>
@@ -12865,7 +12943,7 @@
       </c>
       <c r="H579" s="8"/>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A580" s="5">
         <v>43132</v>
       </c>
@@ -12889,7 +12967,7 @@
       </c>
       <c r="H580" s="8"/>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A581" s="5">
         <v>43160</v>
       </c>
@@ -12913,7 +12991,7 @@
       </c>
       <c r="H581" s="8"/>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A582" s="5">
         <v>43191</v>
       </c>
@@ -12937,7 +13015,7 @@
       </c>
       <c r="H582" s="8"/>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A583" s="5">
         <v>43221</v>
       </c>
@@ -12961,7 +13039,7 @@
       </c>
       <c r="H583" s="8"/>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A584" s="5">
         <v>43252</v>
       </c>
@@ -12985,7 +13063,7 @@
       </c>
       <c r="H584" s="8"/>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A585" s="5">
         <v>43282</v>
       </c>
@@ -13009,7 +13087,7 @@
       </c>
       <c r="H585" s="8"/>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A586" s="5">
         <v>43313</v>
       </c>
@@ -13033,7 +13111,7 @@
       </c>
       <c r="H586" s="8"/>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A587" s="5">
         <v>43344</v>
       </c>
@@ -13057,7 +13135,7 @@
       </c>
       <c r="H587" s="8"/>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A588" s="5">
         <v>43374</v>
       </c>
@@ -13081,7 +13159,7 @@
       </c>
       <c r="H588" s="8"/>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A589" s="5">
         <v>43405</v>
       </c>
@@ -13105,7 +13183,7 @@
       </c>
       <c r="H589" s="8"/>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A590" s="5">
         <v>43435</v>
       </c>
@@ -13129,7 +13207,7 @@
       </c>
       <c r="H590" s="8"/>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A591" s="5">
         <v>43466</v>
       </c>
@@ -13153,7 +13231,7 @@
       </c>
       <c r="H591" s="8"/>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A592" s="5">
         <v>43497</v>
       </c>
@@ -13177,7 +13255,7 @@
       </c>
       <c r="H592" s="8"/>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A593" s="5">
         <v>43525</v>
       </c>
@@ -13201,7 +13279,7 @@
       </c>
       <c r="H593" s="8"/>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A594" s="5">
         <v>43556</v>
       </c>
@@ -13225,7 +13303,7 @@
       </c>
       <c r="H594" s="8"/>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A595" s="5">
         <v>43586</v>
       </c>
@@ -13249,7 +13327,7 @@
       </c>
       <c r="H595" s="8"/>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A596" s="5">
         <v>43617</v>
       </c>
@@ -13273,7 +13351,7 @@
       </c>
       <c r="H596" s="8"/>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A597" s="5">
         <v>43647</v>
       </c>
@@ -13297,7 +13375,7 @@
       </c>
       <c r="H597" s="8"/>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A598" s="5">
         <v>43678</v>
       </c>
@@ -13321,7 +13399,7 @@
       </c>
       <c r="H598" s="8"/>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A599" s="5">
         <v>43709</v>
       </c>
@@ -13345,7 +13423,7 @@
       </c>
       <c r="H599" s="8"/>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A600" s="5">
         <v>43739</v>
       </c>
@@ -13369,7 +13447,7 @@
       </c>
       <c r="H600" s="8"/>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A601" s="5">
         <v>43770</v>
       </c>
@@ -13393,7 +13471,7 @@
       </c>
       <c r="H601" s="8"/>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A602" s="5">
         <v>43800</v>
       </c>
@@ -13417,7 +13495,7 @@
       </c>
       <c r="H602" s="8"/>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A603" s="5">
         <v>43831</v>
       </c>
@@ -13441,7 +13519,7 @@
       </c>
       <c r="H603" s="8"/>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A604" s="5">
         <v>43862</v>
       </c>
@@ -13465,7 +13543,7 @@
       </c>
       <c r="H604" s="8"/>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A605" s="5">
         <v>43891</v>
       </c>
@@ -13489,7 +13567,7 @@
       </c>
       <c r="H605" s="8"/>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A606" s="5">
         <v>43922</v>
       </c>
@@ -13513,7 +13591,7 @@
       </c>
       <c r="H606" s="8"/>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A607" s="5">
         <v>43952</v>
       </c>
@@ -13537,7 +13615,7 @@
       </c>
       <c r="H607" s="8"/>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A608" s="5">
         <v>43983</v>
       </c>
@@ -13561,7 +13639,7 @@
       </c>
       <c r="H608" s="8"/>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A609" s="5">
         <v>44013</v>
       </c>
@@ -13585,7 +13663,7 @@
       </c>
       <c r="H609" s="8"/>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A610" s="5">
         <v>44044</v>
       </c>
@@ -13609,7 +13687,7 @@
       </c>
       <c r="H610" s="8"/>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A611" s="5">
         <v>44075</v>
       </c>
@@ -13633,7 +13711,7 @@
       </c>
       <c r="H611" s="8"/>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A612" s="5">
         <v>44105</v>
       </c>
@@ -13657,7 +13735,7 @@
       </c>
       <c r="H612" s="8"/>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A613" s="5">
         <v>44136</v>
       </c>
@@ -13681,7 +13759,7 @@
       </c>
       <c r="H613" s="8"/>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A614" s="5">
         <v>44166</v>
       </c>
@@ -13705,7 +13783,7 @@
       </c>
       <c r="H614" s="8"/>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A615" s="5">
         <v>44197</v>
       </c>
@@ -13729,7 +13807,7 @@
       </c>
       <c r="H615" s="8"/>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A616" s="5">
         <v>44228</v>
       </c>
@@ -13753,7 +13831,7 @@
       </c>
       <c r="H616" s="8"/>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A617" s="5">
         <v>44256</v>
       </c>
@@ -13777,7 +13855,7 @@
       </c>
       <c r="H617" s="8"/>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A618" s="5">
         <v>44287</v>
       </c>
@@ -13801,7 +13879,7 @@
       </c>
       <c r="H618" s="8"/>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A619" s="5">
         <v>44317</v>
       </c>
@@ -13825,7 +13903,7 @@
       </c>
       <c r="H619" s="8"/>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A620" s="5">
         <v>44348</v>
       </c>
@@ -13849,7 +13927,7 @@
       </c>
       <c r="H620" s="8"/>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A621" s="5">
         <v>44378</v>
       </c>
@@ -13873,7 +13951,7 @@
       </c>
       <c r="H621" s="8"/>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A622" s="5">
         <v>44409</v>
       </c>
@@ -13897,7 +13975,7 @@
       </c>
       <c r="H622" s="8"/>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A623" s="5">
         <v>44440</v>
       </c>
@@ -13921,7 +13999,7 @@
       </c>
       <c r="H623" s="8"/>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A624" s="5">
         <v>44470</v>
       </c>
@@ -13945,7 +14023,7 @@
       </c>
       <c r="H624" s="8"/>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A625" s="5">
         <v>44501</v>
       </c>
@@ -13969,7 +14047,7 @@
       </c>
       <c r="H625" s="8"/>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A626" s="5">
         <v>44531</v>
       </c>
@@ -13993,7 +14071,7 @@
       </c>
       <c r="H626" s="8"/>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A627" s="5">
         <v>44562</v>
       </c>
@@ -14017,7 +14095,7 @@
       </c>
       <c r="H627" s="8"/>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A628" s="5">
         <v>44593</v>
       </c>
@@ -14041,7 +14119,7 @@
       </c>
       <c r="H628" s="8"/>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A629" s="5">
         <v>44621</v>
       </c>
@@ -14065,7 +14143,7 @@
       </c>
       <c r="H629" s="8"/>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A630" s="5">
         <v>44652</v>
       </c>
@@ -14089,7 +14167,7 @@
       </c>
       <c r="H630" s="8"/>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A631" s="5">
         <v>44682</v>
       </c>
@@ -14113,7 +14191,7 @@
       </c>
       <c r="H631" s="8"/>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A632" s="5">
         <v>44713</v>
       </c>
@@ -14137,7 +14215,7 @@
       </c>
       <c r="H632" s="8"/>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A633" s="5">
         <v>44743</v>
       </c>
@@ -14161,7 +14239,7 @@
       </c>
       <c r="H633" s="8"/>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A634" s="5">
         <v>44774</v>
       </c>
@@ -14185,7 +14263,7 @@
       </c>
       <c r="H634" s="8"/>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A635" s="5">
         <v>44805</v>
       </c>
@@ -14209,7 +14287,7 @@
       </c>
       <c r="H635" s="8"/>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A636" s="5">
         <v>44835</v>
       </c>
@@ -14233,7 +14311,7 @@
       </c>
       <c r="H636" s="8"/>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A637" s="5">
         <v>44866</v>
       </c>
@@ -14257,7 +14335,7 @@
       </c>
       <c r="H637" s="8"/>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A638" s="5">
         <v>44896</v>
       </c>
@@ -14281,7 +14359,7 @@
       </c>
       <c r="H638" s="8"/>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A639" s="5">
         <v>44927</v>
       </c>
@@ -14305,7 +14383,7 @@
       </c>
       <c r="H639" s="8"/>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A640" s="5">
         <v>44958</v>
       </c>
@@ -14329,7 +14407,7 @@
       </c>
       <c r="H640" s="8"/>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A641" s="5">
         <v>44986</v>
       </c>
@@ -14353,7 +14431,7 @@
       </c>
       <c r="H641" s="8"/>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A642" s="5">
         <v>45017</v>
       </c>
@@ -14377,7 +14455,7 @@
       </c>
       <c r="H642" s="8"/>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A643" s="5">
         <v>45047</v>
       </c>
@@ -14401,7 +14479,7 @@
       </c>
       <c r="H643" s="8"/>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A644" s="5">
         <v>45078</v>
       </c>
@@ -14425,7 +14503,7 @@
       </c>
       <c r="H644" s="8"/>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A645" s="5">
         <v>45108</v>
       </c>
@@ -14449,7 +14527,7 @@
       </c>
       <c r="H645" s="8"/>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A646" s="5">
         <v>45139</v>
       </c>
@@ -14473,7 +14551,7 @@
       </c>
       <c r="H646" s="8"/>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A647" s="5">
         <v>45170</v>
       </c>
@@ -14497,7 +14575,7 @@
       </c>
       <c r="H647" s="8"/>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A648" s="5">
         <v>45200</v>
       </c>
@@ -14521,7 +14599,7 @@
       </c>
       <c r="H648" s="8"/>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A649" s="5">
         <v>45231</v>
       </c>
@@ -14545,7 +14623,7 @@
       </c>
       <c r="H649" s="8"/>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A650" s="5">
         <v>45261</v>
       </c>
@@ -14569,7 +14647,7 @@
       </c>
       <c r="H650" s="8"/>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A651" s="5">
         <v>45292</v>
       </c>
@@ -14593,7 +14671,7 @@
       </c>
       <c r="H651" s="8"/>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A652" s="5">
         <v>45323</v>
       </c>
@@ -14617,7 +14695,7 @@
       </c>
       <c r="H652" s="8"/>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A653" s="5">
         <v>45352</v>
       </c>
@@ -14641,7 +14719,7 @@
       </c>
       <c r="H653" s="8"/>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A654" s="5">
         <v>45383</v>
       </c>
@@ -14665,7 +14743,7 @@
       </c>
       <c r="H654" s="8"/>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A655" s="5">
         <v>45413</v>
       </c>
@@ -14689,7 +14767,7 @@
       </c>
       <c r="H655" s="8"/>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A656" s="5">
         <v>45444</v>
       </c>
@@ -14713,7 +14791,7 @@
       </c>
       <c r="H656" s="8"/>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A657" s="5">
         <v>45474</v>
       </c>
@@ -14737,7 +14815,7 @@
       </c>
       <c r="H657" s="8"/>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A658" s="5">
         <v>45505</v>
       </c>
@@ -14761,7 +14839,7 @@
       </c>
       <c r="H658" s="8"/>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A659" s="5">
         <v>45536</v>
       </c>
@@ -14782,7 +14860,7 @@
       </c>
       <c r="H659" s="8"/>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A660" s="5">
         <v>45566</v>
       </c>
@@ -14806,7 +14884,7 @@
       </c>
       <c r="H660" s="8"/>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A661" s="5">
         <v>45597</v>
       </c>
@@ -14830,7 +14908,7 @@
       </c>
       <c r="H661" s="8"/>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A662" s="5">
         <v>45627</v>
       </c>
@@ -14854,7 +14932,7 @@
       </c>
       <c r="H662" s="8"/>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A663" s="5">
         <v>45658</v>
       </c>
@@ -14878,7 +14956,7 @@
       </c>
       <c r="H663" s="8"/>
     </row>
-    <row r="664" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A664" s="5">
         <v>45689</v>
       </c>
@@ -14902,7 +14980,7 @@
       </c>
       <c r="H664" s="8"/>
     </row>
-    <row r="665" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A665" s="5">
         <v>45717</v>
       </c>
@@ -14926,7 +15004,7 @@
       </c>
       <c r="H665" s="8"/>
     </row>
-    <row r="666" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A666" s="5">
         <v>45748</v>
       </c>
@@ -14950,7 +15028,7 @@
       </c>
       <c r="H666" s="8"/>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A667" s="5">
         <v>45778</v>
       </c>
@@ -14974,7 +15052,7 @@
       </c>
       <c r="H667" s="8"/>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A668" s="5">
         <v>45809</v>
       </c>
@@ -14998,7 +15076,7 @@
       </c>
       <c r="H668" s="8"/>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A669" s="5">
         <v>45839</v>
       </c>
@@ -15022,7 +15100,7 @@
       </c>
       <c r="H669" s="8"/>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A670" s="5">
         <v>45870</v>
       </c>
@@ -15046,7 +15124,7 @@
       </c>
       <c r="H670" s="8"/>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A671" s="5">
         <v>45901</v>
       </c>
@@ -15070,7 +15148,7 @@
       </c>
       <c r="H671" s="8"/>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A672" s="5">
         <v>45931</v>
       </c>
@@ -15094,7 +15172,7 @@
       </c>
       <c r="H672" s="8"/>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A673" s="5">
         <v>45962</v>
       </c>
@@ -15115,7 +15193,7 @@
       </c>
       <c r="H673" s="8"/>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A674" s="5">
         <v>45992</v>
       </c>
@@ -15139,7 +15217,7 @@
       </c>
       <c r="H674" s="8"/>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A675" s="5">
         <v>46023</v>
       </c>
@@ -15163,7 +15241,7 @@
       </c>
       <c r="H675" s="8"/>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A676" s="5">
         <v>46054</v>
       </c>
@@ -15187,7 +15265,7 @@
       </c>
       <c r="H676" s="8"/>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A677" s="5">
         <v>46082</v>
       </c>
@@ -15211,7 +15289,7 @@
       </c>
       <c r="H677" s="8"/>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A678" s="5">
         <v>46113</v>
       </c>
@@ -15235,7 +15313,7 @@
       </c>
       <c r="H678" s="8"/>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A679" s="5">
         <v>46143</v>
       </c>
@@ -15259,7 +15337,7 @@
       </c>
       <c r="H679" s="8"/>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A680" s="5">
         <v>46174</v>
       </c>
@@ -15283,7 +15361,7 @@
       </c>
       <c r="H680" s="8"/>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A681" s="5">
         <v>46204</v>
       </c>
@@ -15304,6 +15382,29 @@
       </c>
       <c r="G681" s="11">
         <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A682" s="5">
+        <v>46235</v>
+      </c>
+      <c r="B682" s="5">
+        <v>46267</v>
+      </c>
+      <c r="C682" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E682" s="11">
+        <v>3.1E-2</v>
+      </c>
+      <c r="F682" s="11">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="G682" s="11">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -15313,4 +15414,65 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3D879BE-58C9-F24A-A1BF-CB3552E18117}">
+  <dimension ref="B2:G3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="8.83203125" style="4"/>
+    <col min="4" max="4" width="73.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="4"/>
+    <col min="7" max="7" width="10.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B2" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B3" s="13">
+        <v>1</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1" xr:uid="{7E7858E4-697D-3E4A-90B9-A07015F2E100}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>